--- a/wwwroot/templates/MAU EXPORT LICH PHAN CONG COI THI.xlsx
+++ b/wwwroot/templates/MAU EXPORT LICH PHAN CONG COI THI.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\duyentth\Study\DATN\ExamInvigilationManagement\wwwroot\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14AB6AB0-D0FA-4B8E-81B2-DA4C537E5BC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4915FE9-2BBC-43C9-9747-10DAF48EA505}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{5FC086B7-5841-4EFD-A661-700D4A2647D6}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="qlketquaxeplichthi" sheetId="2" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">qlketquaxeplichthi!$A$4:$T$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">qlketquaxeplichthi!$A$4:$R$4</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
   <si>
     <t>BỘ GIÁO DỤC VÀ ĐÀO TẠO</t>
   </si>
@@ -61,12 +61,6 @@
   </si>
   <si>
     <t>Tín chỉ</t>
-  </si>
-  <si>
-    <t>Được sử dụng tài liệu</t>
-  </si>
-  <si>
-    <t>Nhóm thi</t>
   </si>
   <si>
     <t>Nhóm HP</t>
@@ -986,30 +980,29 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2BBD2721-BACE-4EC4-B385-DE7BB8261236}">
-  <dimension ref="A1:T4"/>
+  <dimension ref="A1:R4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3.5703125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="7" customWidth="1"/>
     <col min="3" max="3" width="21.42578125" customWidth="1"/>
-    <col min="4" max="4" width="14.140625" customWidth="1"/>
-    <col min="5" max="5" width="6.140625" hidden="1" customWidth="1"/>
-    <col min="6" max="6" width="18.140625" hidden="1" customWidth="1"/>
-    <col min="7" max="8" width="8" hidden="1" customWidth="1"/>
-    <col min="9" max="9" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="9" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="6.85546875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="0" hidden="1" customWidth="1"/>
-    <col min="15" max="15" width="4.85546875" hidden="1" customWidth="1"/>
-    <col min="16" max="16" width="25.140625" customWidth="1"/>
-    <col min="17" max="18" width="22.28515625" hidden="1" customWidth="1"/>
-    <col min="19" max="19" width="25" customWidth="1"/>
-    <col min="20" max="20" width="24.5703125" customWidth="1"/>
+    <col min="4" max="4" width="19" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="6.85546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="0" hidden="1" customWidth="1"/>
+    <col min="13" max="13" width="4.85546875" hidden="1" customWidth="1"/>
+    <col min="14" max="14" width="25.140625" customWidth="1"/>
+    <col min="15" max="16" width="22.28515625" hidden="1" customWidth="1"/>
+    <col min="17" max="17" width="25" customWidth="1"/>
+    <col min="18" max="18" width="24.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1032,10 +1025,8 @@
       <c r="P1" s="3"/>
       <c r="Q1" s="3"/>
       <c r="R1" s="3"/>
-      <c r="S1" s="3"/>
-      <c r="T1" s="3"/>
     </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
@@ -1058,10 +1049,8 @@
       <c r="P2" s="3"/>
       <c r="Q2" s="3"/>
       <c r="R2" s="3"/>
-      <c r="S2" s="3"/>
-      <c r="T2" s="3"/>
     </row>
-    <row r="3" spans="1:20" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:18" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="4"/>
       <c r="B3" s="4"/>
       <c r="C3" s="4"/>
@@ -1080,10 +1069,8 @@
       <c r="P3" s="4"/>
       <c r="Q3" s="4"/>
       <c r="R3" s="4"/>
-      <c r="S3" s="4"/>
-      <c r="T3" s="4"/>
     </row>
-    <row r="4" spans="1:20" ht="22.5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:18" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>4</v>
       </c>
@@ -1138,21 +1125,15 @@
       <c r="R4" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="S4" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="T4" s="1" t="s">
-        <v>23</v>
-      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:T4" xr:uid="{17C591F3-63A7-4C50-BAEF-8B16D4858D44}"/>
+  <autoFilter ref="A4:R4" xr:uid="{17C591F3-63A7-4C50-BAEF-8B16D4858D44}"/>
   <mergeCells count="5">
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="A2:C2"/>
-    <mergeCell ref="D1:T1"/>
-    <mergeCell ref="D2:T2"/>
-    <mergeCell ref="A3:T3"/>
+    <mergeCell ref="D1:R1"/>
+    <mergeCell ref="D2:R2"/>
+    <mergeCell ref="A3:R3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
